--- a/Test Design/API_Test_Cases.xlsx
+++ b/Test Design/API_Test_Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FARZAN\Desktop\API_Testing_RestfulBooker\Test Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFD70DF-8368-4950-8D5B-0749E54FFA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECBF5060-D3FD-413D-B4FE-7FF8E4B9282D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="296">
   <si>
     <t>Status</t>
   </si>
@@ -485,9 +485,6 @@
 }</t>
   </si>
   <si>
-    <t>HTTP 401 Unauthorized</t>
-  </si>
-  <si>
     <t xml:space="preserve">Verify booking update fails with expired or invalid auth token </t>
   </si>
   <si>
@@ -496,9 +493,6 @@
   <si>
     <t>Headers:
 Cookie: token=invalid_token123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP 401 Unauthorized </t>
   </si>
   <si>
     <t>Verify booking update fails with partial payload missing mandatory field</t>
@@ -636,9 +630,6 @@
   </si>
   <si>
     <t>Send DELETE request to booking/:id without auth token</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HTTP 401 Unauthorized</t>
   </si>
   <si>
     <t>Verify deletion fails for non existent booking ID</t>
@@ -870,12 +861,6 @@
     <t>API returns HTTP 404 Not Found as expected</t>
   </si>
   <si>
-    <t>API returned HTTP 403 Forbidden instead of the expected HTTP 401 Unauthorized</t>
-  </si>
-  <si>
-    <t>API returned HTTP 403 Forbidden instead of the HTTP 401 Unauthorized</t>
-  </si>
-  <si>
     <t>API returned HTTP 400 Bad Request as expected</t>
   </si>
   <si>
@@ -886,9 +871,6 @@
   </si>
   <si>
     <t>API returned HTTP 200 OK as expected and Response body contains booking details and only 'totalprice' is changed to 999</t>
-  </si>
-  <si>
-    <t>API returned HTTP 403 Forbidden instead of the expected HTTP 401 Unauthoriized</t>
   </si>
   <si>
     <t>API returned HTTP 405 Method Not Allowed instead of the expected HTTP 404 Not Found</t>
@@ -1114,15 +1096,34 @@
   <si>
     <t>HTTP 201 Created and Time taken is &lt;3000ms</t>
   </si>
+  <si>
+    <t>HTTP 403 Forbidden</t>
+  </si>
+  <si>
+    <t>API returned HTTP 403 Forbidden as expected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 403 Forbidden </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HTTP 403 Forbidden</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1222,7 +1223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1230,40 +1231,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1272,16 +1273,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1617,13 +1621,13 @@
   <sheetData>
     <row r="1" spans="1:11" s="3" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
@@ -1632,19 +1636,19 @@
         <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>0</v>
@@ -1652,22 +1656,22 @@
     </row>
     <row r="2" spans="1:11" ht="28.8">
       <c r="A2" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>5</v>
@@ -1678,16 +1682,16 @@
       <c r="I2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="20" t="s">
-        <v>201</v>
+      <c r="J2" s="21" t="s">
+        <v>198</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="28.8">
       <c r="F3" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>7</v>
@@ -1696,27 +1700,27 @@
         <v>8</v>
       </c>
       <c r="I3" s="13"/>
-      <c r="J3" s="20"/>
+      <c r="J3" s="21"/>
       <c r="K3" s="15"/>
     </row>
     <row r="4" spans="1:11" ht="28.8">
       <c r="A4" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>11</v>
@@ -1728,15 +1732,15 @@
         <v>14</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="28.8">
       <c r="F5" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>12</v>
@@ -1750,22 +1754,22 @@
     </row>
     <row r="6" spans="1:11" ht="28.8">
       <c r="A6" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>11</v>
@@ -1777,15 +1781,15 @@
         <v>19</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="F7" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
@@ -1799,22 +1803,22 @@
     </row>
     <row r="8" spans="1:11" ht="28.8">
       <c r="A8" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>11</v>
@@ -1826,15 +1830,15 @@
         <v>23</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="F9" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>21</v>
@@ -1848,22 +1852,22 @@
     </row>
     <row r="10" spans="1:11" ht="57.6">
       <c r="A10" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>26</v>
@@ -1875,15 +1879,15 @@
         <v>30</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="158.4">
       <c r="F11" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>28</v>
@@ -1897,22 +1901,22 @@
     </row>
     <row r="12" spans="1:11" ht="43.2">
       <c r="A12" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>26</v>
@@ -1924,15 +1928,15 @@
         <v>34</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="144">
       <c r="F13" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>32</v>
@@ -1946,22 +1950,22 @@
     </row>
     <row r="14" spans="1:11" ht="28.8">
       <c r="A14" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>26</v>
@@ -1970,18 +1974,18 @@
         <v>6</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="158.4">
       <c r="F15" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>36</v>
@@ -1995,22 +1999,22 @@
     </row>
     <row r="16" spans="1:11" ht="28.8">
       <c r="A16" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>26</v>
@@ -2022,15 +2026,15 @@
         <v>41</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="158.4">
       <c r="F17" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>39</v>
@@ -2044,22 +2048,22 @@
     </row>
     <row r="18" spans="1:11" ht="43.2">
       <c r="A18" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>26</v>
@@ -2071,15 +2075,15 @@
         <v>45</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="158.4">
       <c r="F19" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>43</v>
@@ -2093,22 +2097,22 @@
     </row>
     <row r="20" spans="1:11" ht="43.2">
       <c r="A20" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>26</v>
@@ -2120,15 +2124,15 @@
         <v>45</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="158.4">
       <c r="F21" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>48</v>
@@ -2142,22 +2146,22 @@
     </row>
     <row r="22" spans="1:11" ht="28.8">
       <c r="A22" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>26</v>
@@ -2169,15 +2173,15 @@
         <v>45</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="158.4">
       <c r="F23" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>52</v>
@@ -2191,22 +2195,22 @@
     </row>
     <row r="24" spans="1:11" ht="28.8">
       <c r="A24" s="1" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>26</v>
@@ -2215,18 +2219,18 @@
         <v>51</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="158.4">
       <c r="F25" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>55</v>
@@ -2240,22 +2244,22 @@
     </row>
     <row r="26" spans="1:11" ht="43.2">
       <c r="A26" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>26</v>
@@ -2264,18 +2268,18 @@
         <v>51</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="158.4">
       <c r="F27" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>58</v>
@@ -2289,22 +2293,22 @@
     </row>
     <row r="28" spans="1:11" ht="43.2">
       <c r="A28" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>26</v>
@@ -2316,15 +2320,15 @@
         <v>45</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="244.8">
       <c r="F29" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>62</v>
@@ -2338,57 +2342,57 @@
     </row>
     <row r="30" spans="1:11" ht="28.8">
       <c r="A30" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>60</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="43.2" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>68</v>
@@ -2397,18 +2401,18 @@
         <v>69</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="F32" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>70</v>
@@ -2422,22 +2426,22 @@
     </row>
     <row r="33" spans="1:11" ht="28.8">
       <c r="A33" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>72</v>
@@ -2446,18 +2450,18 @@
         <v>73</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="F34" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>74</v>
@@ -2471,22 +2475,22 @@
     </row>
     <row r="35" spans="1:11" ht="28.8">
       <c r="A35" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>76</v>
@@ -2495,18 +2499,18 @@
         <v>77</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="J35" s="18" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="F36" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>78</v>
@@ -2520,22 +2524,22 @@
     </row>
     <row r="37" spans="1:11" ht="28.8">
       <c r="A37" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>80</v>
@@ -2544,18 +2548,18 @@
         <v>81</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="J37" s="18" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="F38" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>78</v>
@@ -2569,22 +2573,22 @@
     </row>
     <row r="39" spans="1:11" ht="43.2">
       <c r="A39" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>83</v>
@@ -2596,30 +2600,30 @@
         <v>60</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="28.8">
       <c r="A40" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>85</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>86</v>
@@ -2631,18 +2635,18 @@
         <v>88</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="43.2">
       <c r="A41" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>89</v>
@@ -2654,7 +2658,7 @@
         <v>25</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>91</v>
@@ -2666,18 +2670,18 @@
         <v>88</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="28.8">
       <c r="A42" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>93</v>
@@ -2689,7 +2693,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>95</v>
@@ -2701,15 +2705,15 @@
         <v>60</v>
       </c>
       <c r="J42" s="18" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="158.4">
       <c r="F43" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>97</v>
@@ -2723,10 +2727,10 @@
     </row>
     <row r="44" spans="1:11" ht="43.2">
       <c r="A44" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>99</v>
@@ -2738,7 +2742,7 @@
         <v>25</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>101</v>
@@ -2747,18 +2751,18 @@
         <v>102</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="J44" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="K44" s="16" t="s">
-        <v>241</v>
+        <v>292</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="158.4">
       <c r="F45" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>103</v>
@@ -2768,17 +2772,17 @@
       </c>
       <c r="I45" s="13"/>
       <c r="J45" s="18"/>
-      <c r="K45" s="16"/>
+      <c r="K45" s="15"/>
     </row>
     <row r="46" spans="1:11" ht="28.8">
       <c r="A46" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>100</v>
@@ -2787,27 +2791,27 @@
         <v>25</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G46" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H46" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="I46" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="J46" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="K46" s="16" t="s">
-        <v>241</v>
+        <v>294</v>
+      </c>
+      <c r="J46" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="158.4">
       <c r="F47" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>103</v>
@@ -2817,17 +2821,17 @@
       </c>
       <c r="I47" s="13"/>
       <c r="J47" s="18"/>
-      <c r="K47" s="16"/>
+      <c r="K47" s="15"/>
     </row>
     <row r="48" spans="1:11" ht="43.2">
       <c r="A48" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>94</v>
@@ -2836,33 +2840,33 @@
         <v>25</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>95</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I48" s="13" t="s">
         <v>45</v>
       </c>
       <c r="J48" s="18" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="144">
       <c r="F49" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I49" s="13"/>
       <c r="J49" s="18"/>
@@ -2870,42 +2874,42 @@
     </row>
     <row r="50" spans="1:11" ht="28.8">
       <c r="A50" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G50" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I50" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="H50" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I50" s="13" t="s">
-        <v>118</v>
-      </c>
       <c r="J50" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="158.4">
       <c r="F51" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>103</v>
@@ -2919,48 +2923,48 @@
     </row>
     <row r="52" spans="1:11" ht="43.2">
       <c r="A52" s="1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I52" s="13" t="s">
         <v>60</v>
       </c>
       <c r="J52" s="18" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="F53" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I53" s="13"/>
       <c r="J53" s="18"/>
@@ -2968,48 +2972,48 @@
     </row>
     <row r="54" spans="1:11" ht="28.8">
       <c r="A54" s="1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="J54" s="18" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="F55" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I55" s="13"/>
       <c r="J55" s="18"/>
@@ -3017,10 +3021,10 @@
     </row>
     <row r="56" spans="1:11">
       <c r="F56" s="1" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>66</v>
@@ -3031,13 +3035,13 @@
     </row>
     <row r="57" spans="1:11" ht="28.8">
       <c r="A57" s="1" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>100</v>
@@ -3046,82 +3050,82 @@
         <v>25</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="J57" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="K57" s="16" t="s">
-        <v>241</v>
+        <v>292</v>
+      </c>
+      <c r="J57" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="K57" s="15" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="F58" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I58" s="13"/>
       <c r="J58" s="18"/>
-      <c r="K58" s="16"/>
+      <c r="K58" s="15"/>
     </row>
     <row r="59" spans="1:11" ht="28.8">
       <c r="A59" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>88</v>
       </c>
       <c r="J59" s="18" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="K59" s="16" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="F60" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I60" s="13"/>
       <c r="J60" s="18"/>
@@ -3129,48 +3133,48 @@
     </row>
     <row r="61" spans="1:11" ht="43.2">
       <c r="A61" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J61" s="18" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="F62" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I62" s="13"/>
       <c r="J62" s="18"/>
@@ -3178,129 +3182,129 @@
     </row>
     <row r="63" spans="1:11" ht="28.8">
       <c r="A63" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>88</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="28.8">
       <c r="A64" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="J64" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="K64" s="16" t="s">
-        <v>241</v>
+        <v>295</v>
+      </c>
+      <c r="J64" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="K64" s="15" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="F65" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I65" s="13"/>
       <c r="J65" s="18"/>
-      <c r="K65" s="16"/>
+      <c r="K65" s="15"/>
     </row>
     <row r="66" spans="1:11" ht="28.8">
       <c r="A66" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I66" s="13" t="s">
         <v>88</v>
       </c>
       <c r="J66" s="18" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="K66" s="16" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="F67" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>87</v>
@@ -3311,48 +3315,48 @@
     </row>
     <row r="68" spans="1:11" ht="28.8">
       <c r="A68" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I68" s="13" t="s">
         <v>88</v>
       </c>
       <c r="J68" s="18" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="K68" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="F69" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I69" s="13"/>
       <c r="J69" s="18"/>
@@ -3360,72 +3364,72 @@
     </row>
     <row r="70" spans="1:11" s="9" customFormat="1" ht="28.8">
       <c r="A70" s="10" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>25</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>66</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="K70" s="12" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="9" customFormat="1" ht="43.2" customHeight="1">
       <c r="A71" s="10" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>25</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H71" s="9" t="s">
         <v>66</v>
       </c>
       <c r="I71" s="14" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="J71" s="19" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="K71" s="17" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="9" customFormat="1">
@@ -3433,10 +3437,10 @@
       <c r="B72" s="10"/>
       <c r="E72" s="10"/>
       <c r="F72" s="10" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H72" s="9" t="s">
         <v>66</v>
@@ -3447,120 +3451,120 @@
     </row>
     <row r="73" spans="1:11" ht="158.4">
       <c r="A73" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="28.8">
       <c r="F74" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K74" s="15"/>
     </row>
     <row r="75" spans="1:11" ht="57.6">
       <c r="F75" s="1" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="K75" s="15"/>
     </row>
     <row r="76" spans="1:11" ht="28.8">
       <c r="F76" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="K76" s="15"/>
     </row>
     <row r="77" spans="1:11">
       <c r="F77" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>88</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="K77" s="15"/>
     </row>
     <row r="78" spans="1:11" ht="172.8">
       <c r="A78" s="1" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>16</v>
@@ -3569,57 +3573,57 @@
         <v>25</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="28.8">
       <c r="F79" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>60</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K79" s="15"/>
     </row>
     <row r="80" spans="1:11" ht="28.8">
       <c r="F80" s="1" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>66</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="K80" s="15"/>
     </row>
